--- a/order_forms/037_customized_apron_order_form--order_forms.xlsx
+++ b/order_forms/037_customized_apron_order_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Category 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>assigned_tool_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Assigned Tool 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>output_file_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Output File</t>
+          <t>Output File 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>customer_details</t>
+          <t>customer_details_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Customer Details</t>
+          <t>Customer Details 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>customer_email</t>
+          <t>customer_email_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Customer Email</t>
+          <t>Customer Email 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>customer_phone</t>
+          <t>customer_phone_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Customer Phone</t>
+          <t>Customer Phone 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>customer_name</t>
+          <t>customer_name_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Customer Name</t>
+          <t>Customer Name 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>form_id_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Form ID</t>
+          <t>Form Id 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>apron_style_black</t>
+          <t>apron style black</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>apron_style_blue</t>
+          <t>apron style blue</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>apron_style_red</t>
+          <t>apron style red</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>color_white</t>
+          <t>color white</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>color_black</t>
+          <t>color black</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>color_blue</t>
+          <t>color blue</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>customization_name_1</t>
+          <t>customization name 1</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>customization_name_2</t>
+          <t>customization name 2</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>customization_name_3</t>
+          <t>customization name 3</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>order_forms</t>
+          <t>order forms</t>
         </is>
       </c>
     </row>
@@ -1335,19 +1335,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>order_forms</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>order_forms</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1357,31 +1357,31 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>order_forms</t>
+          <t>order forms</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>order_forms</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>order_forms</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>assigned_tool_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1398,7 +1398,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>assigned_tool_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
